--- a/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 9,33</t>
+          <t>-8,14; 9,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 8,41</t>
+          <t>-8,84; 7,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 9,75</t>
+          <t>-6,87; 10,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 22,41</t>
+          <t>-11,92; 22,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-33,51; 64,55</t>
+          <t>-35,12; 60,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 38,84</t>
+          <t>-29,91; 37,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 57,24</t>
+          <t>-26,23; 63,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-66,78; 433,27</t>
+          <t>-64,87; 458,84</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 2,79</t>
+          <t>-5,03; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 3,24</t>
+          <t>-5,58; 2,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 2,09</t>
+          <t>-6,53; 1,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 6,78</t>
+          <t>-8,55; 6,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 49,62</t>
+          <t>-51,45; 56,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,06; 44,89</t>
+          <t>-51,17; 41,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,34; 38,45</t>
+          <t>-61,26; 35,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 5,83</t>
+          <t>-4,06; 5,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 6,0</t>
+          <t>-1,66; 5,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,31</t>
+          <t>-3,93; 3,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,22; 18,58</t>
+          <t>1,27; 18,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,28; 238,88</t>
+          <t>-62,44; 206,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,67; 449,47</t>
+          <t>-44,74; 462,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-59,55; 149,28</t>
+          <t>-63,74; 127,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,59</t>
+          <t>-2,26; 5,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 2,03</t>
+          <t>-4,9; 2,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 8,73</t>
+          <t>-0,94; 8,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 18,59</t>
+          <t>-4,49; 17,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 224,61</t>
+          <t>-41,36; 249,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,47; 101,29</t>
+          <t>-79,43; 101,89</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,01; 401,84</t>
+          <t>-23,98; 350,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,63</t>
+          <t>-2,49; 2,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,54</t>
+          <t>-2,85; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 3,37</t>
+          <t>-1,94; 3,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,46</t>
+          <t>-1,13; 9,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 40,07</t>
+          <t>-25,11; 40,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 28,98</t>
+          <t>-25,08; 30,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,06; 45,02</t>
+          <t>-19,34; 47,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 420,35</t>
+          <t>-28,56; 410,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 9,37</t>
+          <t>-7,59; 9,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 7,93</t>
+          <t>-8,95; 8,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 10,36</t>
+          <t>-6,56; 10,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 22,89</t>
+          <t>-11,57; 21,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,12; 60,53</t>
+          <t>-32,47; 71,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 37,14</t>
+          <t>-29,98; 39,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,23; 63,64</t>
+          <t>-25,78; 64,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 458,84</t>
+          <t>-70,96; 387,87</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 3,19</t>
+          <t>-4,86; 2,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 2,81</t>
+          <t>-5,3; 3,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 1,85</t>
+          <t>-6,25; 1,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 6,62</t>
+          <t>-9,72; 6,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 56,17</t>
+          <t>-49,02; 45,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 41,87</t>
+          <t>-48,7; 42,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,26; 35,46</t>
+          <t>-58,31; 29,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 5,48</t>
+          <t>-3,98; 5,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,85</t>
+          <t>-1,52; 6,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,26</t>
+          <t>-3,87; 2,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,27; 18,3</t>
+          <t>1,28; 19,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,44; 206,35</t>
+          <t>-63,78; 221,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 462,83</t>
+          <t>-41,15; 500,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,74; 127,19</t>
+          <t>-65,5; 117,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 5,93</t>
+          <t>-2,14; 5,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 2,08</t>
+          <t>-5,11; 1,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 8,36</t>
+          <t>-0,86; 9,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 17,5</t>
+          <t>-4,85; 16,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,36; 249,16</t>
+          <t>-41,88; 227,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,43; 101,89</t>
+          <t>-80,77; 83,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 350,31</t>
+          <t>-23,19; 444,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,84</t>
+          <t>-2,42; 2,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 2,66</t>
+          <t>-2,63; 2,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 3,47</t>
+          <t>-1,99; 3,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 9,21</t>
+          <t>-1,09; 8,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 40,48</t>
+          <t>-24,33; 37,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 30,85</t>
+          <t>-22,89; 29,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,34; 47,03</t>
+          <t>-19,62; 42,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 410,84</t>
+          <t>-31,08; 390,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por vacunación</t>
+          <t>Menores cuya última consulta médica fue por vacunación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,39</t>
+          <t>3,74</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>31,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 9,78</t>
+          <t>-8,18; 9,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 8,18</t>
+          <t>-9,36; 8,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 10,85</t>
+          <t>-7,37; 9,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 21,34</t>
+          <t>-11,08; 21,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 71,31</t>
+          <t>-33,51; 64,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 39,32</t>
+          <t>-29,71; 38,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-25,78; 64,75</t>
+          <t>-27,76; 57,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-70,96; 387,87</t>
+          <t>-67,56; 474,86</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-40,78%</t>
+          <t>-31,26%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,56</t>
+          <t>-5,15; 2,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 3,17</t>
+          <t>-5,49; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,82</t>
+          <t>-6,35; 2,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 6,06</t>
+          <t>-7,16; 8,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-49,02; 45,07</t>
+          <t>-51,74; 49,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,7; 42,83</t>
+          <t>-50,06; 44,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 29,83</t>
+          <t>-59,34; 38,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,22</t>
+          <t>6,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 5,69</t>
+          <t>-4,38; 5,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 6,23</t>
+          <t>-2,15; 6,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 2,91</t>
+          <t>-3,5; 3,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,28; 19,18</t>
+          <t>1,16; 19,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,78; 221,47</t>
+          <t>-63,28; 238,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 500,71</t>
+          <t>-51,67; 449,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,5; 117,79</t>
+          <t>-59,55; 149,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,41</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>92,29%</t>
         </is>
       </c>
     </row>
@@ -960,37 +960,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 5,93</t>
+          <t>-2,19; 5,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 1,93</t>
+          <t>-5,12; 2,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 9,07</t>
+          <t>-0,93; 8,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 16,25</t>
+          <t>-4,34; 18,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,88; 227,48</t>
+          <t>-40,68; 224,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-80,77; 83,31</t>
+          <t>-78,47; 101,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 444,32</t>
+          <t>-24,01; 401,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,08</t>
+          <t>3,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>91,59%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,8</t>
+          <t>-2,41; 2,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 2,58</t>
+          <t>-2,91; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 3,19</t>
+          <t>-1,71; 3,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 8,81</t>
+          <t>-1,1; 9,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,33; 37,78</t>
+          <t>-26,3; 40,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 29,32</t>
+          <t>-25,77; 28,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-19,62; 42,47</t>
+          <t>-17,06; 45,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 390,59</t>
+          <t>-29,5; 457,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP18A01-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,74</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.1246900198329542</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.1877673794184576</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.590698071285729</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.73908765014619</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.00635025006927861</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.007342253624493901</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.073325963295611</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.318657458787966</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,18; 9,33</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,36; 8,41</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-7,37; 9,75</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,08; 21,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-33,51; 64,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-29,71; 38,84</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-27,76; 57,24</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-67,56; 474,86</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.177359137235484</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.364187575767973</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-7.368915471529131</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.07852103971407</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.3351188772744129</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2970509424614329</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2775899707337106</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6756330693724231</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.327211349251204</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.412270203547555</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.746320740990729</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>20.99678261877112</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.645484923747367</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3883575167109806</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.5723720884052552</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>4.748563413833309</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-1,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,33</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,21</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-1,31</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-12,74%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-14,68%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-26,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-31,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,15; 2,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-5,49; 3,24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-6,35; 2,09</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 8,72</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-51,74; 49,62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-50,06; 44,89</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-59,34; 38,45</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.013385974949821</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.325555691762712</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.206183987559709</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-1.313601309626676</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1273619600981654</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1467892209394504</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.2641307313388427</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.3125848909649959</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,15</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,71</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>70,14%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-5,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.154213064784058</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-5.488372939415808</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-6.348988143121955</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-7.158670816368662</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5174420024744494</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5005710980764438</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.5934448232988758</v>
+      </c>
+      <c r="J8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,38; 5,83</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,15; 6,0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,5; 3,31</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,16; 19,28</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-63,28; 238,88</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-51,67; 449,47</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-59,55; 149,28</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.78909706296989</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.24331971734932</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.086383384633081</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>8.723293070724097</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4961886596567879</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.4489356893499951</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3845177399916361</v>
+      </c>
+      <c r="J9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,44 +815,30 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,71</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3,77</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,37</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>41,1%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-34,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>92,29%</t>
+      <c r="C10" s="5" t="n">
+        <v>0.5417694493511218</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.152825817428361</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.2477467152734003</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6.706301819494037</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.113963935655977</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.7013621665980259</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.05684341065469754</v>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
         </is>
       </c>
     </row>
@@ -955,152 +846,260 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,19; 5,59</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 2,03</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,93; 8,73</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,34; 18,79</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-40,68; 224,61</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-78,47; 101,29</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-24,01; 401,84</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.381658276582933</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.152790381443037</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.500186562900287</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1.161328488315625</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.632822508179837</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5167261018236734</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.5955324252457027</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.826608528512656</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.995667811185283</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.306034097564611</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>19.27606348032492</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2.388837704145879</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4.494671322751644</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.492761872604528</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>1.713331492205137</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.513866843471171</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>3.773724715761093</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>3.372224257353119</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4110397364865893</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.3443658593963495</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.927620374401108</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.9228617725927634</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.194772239024951</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.123571443295432</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.9262262530044219</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.34203349461935</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4068118571932702</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7847141511245814</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2401181496997711</v>
+      </c>
+      <c r="J14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>5.59332439972184</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.032549143238103</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>8.734309483729161</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>18.79051246030651</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.246057223278889</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.012922118495061</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>4.018403178884578</v>
+      </c>
+      <c r="J15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,42</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,99%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>91,59%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,41; 2,63</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,91; 2,54</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 3,37</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,1; 9,85</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,3; 40,07</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-25,77; 28,98</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-17,06; 45,02</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-29,5; 457,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.1865206089009711</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.199116853063841</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6549749645332823</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>3.422645378771939</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.02230335883997556</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01989680966884111</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.07482316246469671</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.9159230222830604</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.412795972206937</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.914181561081118</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.709905473812558</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.098157685879488</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2629950415362667</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2576581532216187</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.170592426250566</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2950211345951732</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.628549223601048</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.535898748553755</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.374837299810923</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>9.852401927746843</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.4006877900348612</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.2898031412045661</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.4502107027156207</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>4.570886511026245</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1107,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
